--- a/data/test_cases.xlsx
+++ b/data/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aiHermes\api-test-platform\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3C61C3-744E-41D2-820F-A2BE071CD36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D874E5B-3B7A-4761-B71B-BBCDAAE13E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>case_name</t>
   </si>
@@ -93,6 +93,18 @@
   </si>
   <si>
     <t>xbin不在这</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空密码登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"username":"admin","password":""}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>密码错误</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -440,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.453125" customWidth="1"/>
@@ -551,6 +563,26 @@
         <v>21</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>401</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/test_cases.xlsx
+++ b/data/test_cases.xlsx
@@ -1,142 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aiHermes\api-test-platform\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D874E5B-3B7A-4761-B71B-BBCDAAE13E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="登录测试用例" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
-  <si>
-    <t>case_name</t>
-  </si>
-  <si>
-    <t>endpoint</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t>body</t>
-  </si>
-  <si>
-    <t>expected_status</t>
-  </si>
-  <si>
-    <t>expected_msg</t>
-  </si>
-  <si>
-    <t>正常登录</t>
-  </si>
-  <si>
-    <t>/api/login</t>
-  </si>
-  <si>
-    <t>POST</t>
-  </si>
-  <si>
-    <t>登录成功</t>
-  </si>
-  <si>
-    <t>错误密码</t>
-  </si>
-  <si>
-    <t>密码错误</t>
-  </si>
-  <si>
-    <t>用户不存在</t>
-  </si>
-  <si>
-    <t>用户未找到</t>
-  </si>
-  <si>
-    <t>{"username":"admin","password":"123456"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"admin","password":"wrong"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>错错错</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/login</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"nobody","password":"123"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"xbin","password":"122113"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>xbin不在这</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>空密码登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"username":"admin","password":""}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>密码错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -144,26 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -451,140 +420,303 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.453125" customWidth="1"/>
-    <col min="2" max="2" width="19.453125" customWidth="1"/>
-    <col min="3" max="3" width="13.90625" customWidth="1"/>
-    <col min="4" max="4" width="31.90625" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>endpoint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>expected_status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>expected_msg</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>expected_code</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>200</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>正常登录</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>/api/login</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{"username":"admin","password":"123456"}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>登录成功</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>401</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>错误密码</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>/api/login</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{"username":"admin","password":"wrong"}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>密码错误</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4">
-        <v>404</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>用户不存在</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>/api/login</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{"username":"nobody","password":"123"}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>用户未找到</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>404</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>错错错</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>/api/login</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{"username":"xbin","password":"122113"}</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>用户未找到</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>401</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>空密码登录</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>/api/login</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{"username":"admin","password":""}</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>密码错误</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>获取订单列表</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>/api/orders</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>获取成功</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>访问不存在的接口</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>/api/not_exist</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>接口不存在</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/test_cases.xlsx
+++ b/data/test_cases.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>expected_code</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>expected_msg</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>expected_code</t>
         </is>
       </c>
     </row>
@@ -486,19 +486,15 @@
           <t>{"username":"admin","password":"123456"}</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>登录成功</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -523,19 +519,15 @@
           <t>{"username":"admin","password":"wrong"}</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>401</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>密码错误</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-1</t>
         </is>
       </c>
     </row>
@@ -557,22 +549,18 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"username":"nobody","password":"123"}</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>{"username":"not_exist","password":"123456"}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>404</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>用户未找到</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-1</t>
         </is>
       </c>
     </row>
@@ -594,22 +582,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{"username":"xbin","password":"122113"}</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>{"username":"错错错","password":"错错错"}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>404</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>用户未找到</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-1</t>
         </is>
       </c>
     </row>
@@ -634,19 +618,15 @@
           <t>{"username":"admin","password":""}</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>401</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>密码错误</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-1</t>
         </is>
       </c>
     </row>
@@ -666,20 +646,20 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>获取成功</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -699,20 +679,185 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>404</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>接口不存在</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-1</t>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>空body创建订单</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>/api/orders</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>400</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>负金额创建订单</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>/api/orders</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"order_id":"EXCEL_NEG_001","amount":-50}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>400</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>查不存在的订单</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>/api/orders/NONEXIST_BY_EXCEL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>404</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>支付不存在的订单</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>/api/payment/status</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"order_id":"NONEXIST_ORD_999","status":"paid"}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>404</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JSON发送正常</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>/api/edge/empty-body</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"key":"val"}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>

--- a/data/test_cases.xlsx
+++ b/data/test_cases.xlsx
@@ -553,14 +553,14 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F4" t="n">
         <v>-1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>用户未找到</t>
+          <t>用户名或密码错误</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F5" t="n">
         <v>-1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>用户未找到</t>
+          <t>用户名或密码错误</t>
         </is>
       </c>
     </row>

--- a/data/test_cases.xlsx
+++ b/data/test_cases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>expected_msg</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -497,6 +502,11 @@
           <t>登录成功</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -530,6 +540,11 @@
           <t>密码错误</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,6 +578,11 @@
           <t>用户名或密码错误</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,6 +616,11 @@
           <t>用户名或密码错误</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -629,6 +654,11 @@
           <t>密码错误</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -662,6 +692,11 @@
           <t>获取成功</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -695,6 +730,11 @@
           <t>接口不存在</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -728,6 +768,11 @@
           <t>金额</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -761,6 +806,11 @@
           <t>金额</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -794,6 +844,11 @@
           <t>不存在</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -827,6 +882,11 @@
           <t>不存在</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -858,6 +918,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>ok</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
